--- a/AAII_Financials/Yearly/HKXCY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HKXCY_YR_FIN.xlsx
@@ -1715,10 +1715,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>6052100</v>
+        <v>6103700</v>
       </c>
       <c r="E43" s="3">
-        <v>4488800</v>
+        <v>4521900</v>
       </c>
       <c r="F43" s="3">
         <v>3029000</v>
@@ -1781,10 +1781,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>40167800</v>
+        <v>40116200</v>
       </c>
       <c r="E45" s="3">
-        <v>21964700</v>
+        <v>21931600</v>
       </c>
       <c r="F45" s="3">
         <v>18586500</v>
